--- a/public/plantilla-tarifas.xlsx
+++ b/public/plantilla-tarifas.xlsx
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Manilla</t>
+          <t>Producto</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
